--- a/templates/programme-template.xlsx
+++ b/templates/programme-template.xlsx
@@ -466,7 +466,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1. Fill in the Programme sheet: one row per day per fleet (or per event or training session). Delete the sample rows first.</t>
+          <t>1. Fill in the Programme sheet: one row per day per fleet (or per event or training session). In a new copy of the template, delete the sample rows first.</t>
         </is>
       </c>
     </row>
